--- a/public/file/International Tracking Upload Template.xlsx
+++ b/public/file/International Tracking Upload Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Waqas\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{863455C5-07F0-4BCD-95CB-39DD1A62C3F4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB9A88E-4E07-4E64-839B-43C40D55B41C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{EBD77F68-C82E-4F71-9800-F4895BB0818A}"/>
+    <workbookView xWindow="1116" yWindow="912" windowWidth="21600" windowHeight="12048" xr2:uid="{EBD77F68-C82E-4F71-9800-F4895BB0818A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,12 +25,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Tracking Number</t>
   </si>
   <si>
     <t>International Tracking Number</t>
+  </si>
+  <si>
+    <t>Actual Weight</t>
   </si>
 </sst>
 </file>
@@ -383,20 +386,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76606C-1432-4F7F-B1D9-C19C93975332}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.5546875" customWidth="1"/>
     <col min="2" max="2" width="24.88671875" customWidth="1"/>
+    <col min="3" max="3" width="30.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/file/International Tracking Upload Template.xlsx
+++ b/public/file/International Tracking Upload Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB9A88E-4E07-4E64-839B-43C40D55B41C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3077E54D-19D2-42B2-B77C-1D8E6931CAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="912" windowWidth="21600" windowHeight="12048" xr2:uid="{EBD77F68-C82E-4F71-9800-F4895BB0818A}"/>
+    <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{EBD77F68-C82E-4F71-9800-F4895BB0818A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Tracking Number</t>
   </si>
@@ -34,6 +34,9 @@
   </si>
   <si>
     <t>Actual Weight</t>
+  </si>
+  <si>
+    <t>Service Provider</t>
   </si>
 </sst>
 </file>
@@ -386,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76606C-1432-4F7F-B1D9-C19C93975332}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.5546875" customWidth="1"/>
@@ -394,7 +397,7 @@
     <col min="3" max="3" width="30.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -404,6 +407,9 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
